--- a/r5-aist-trustworthyai-poc-pipeline/StructureDefinition-third-country-data-transfer.xlsx
+++ b/r5-aist-trustworthyai-poc-pipeline/StructureDefinition-third-country-data-transfer.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T09:07:35+00:00</t>
+    <t>2026-06-18T11:52:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
